--- a/relatorio_pericias.xlsx
+++ b/relatorio_pericias.xlsx
@@ -808,7 +808,11 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Expertise Cálculos e Perícias Judiciais</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>007.401.374-25</t>
@@ -816,7 +820,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, faltando, apenas, a comprovação de entrega do laudo pericial em cartório, a fim de possibilitar o pagamento respectivo.</t>
+          <t>expertisecpj.doc@gmail.com</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -843,11 +847,7 @@
           <t>005071_46_2025_8_15_SEI_005071_46.2025.8.15.zip</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Sem PERITO</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Kamila Sampaio Nunes Machado</t>
+          <t>Kamila Sampaio Nunes Machado - Médica</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como a comprovação de entrega do laudo pericial em cartório.</t>
+          <t>Interessado:</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Eletricista</t>
+          <t>Engenheira Eletricista</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1718,7 +1718,11 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Ana Roberta Borges da Silva</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>703.933.934-02</t>
@@ -1726,7 +1730,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Ana Roberta Borges da Silva, CPF 703.933.934</t>
+          <t>Entrevistadora Forense – anarobertaborges26@gmail.com</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1747,7 +1751,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -2332,13 +2336,21 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>JOELLEN ZANARDINE CORDEIRO – Engenheira Civil –</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>089.695.184-79</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Engenheira Civil –</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -2357,7 +2369,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2402,11 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Aline Grisi de Lacerda</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>091.447.454-51</t>
@@ -2398,7 +2414,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Aline Grisi de Lacerda, CPF 091.447.454</t>
+          <t>Entrevistadora Forense</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2419,7 +2435,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2836,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Médico Psiquiatra</t>
+          <t>Médico Psiquiatra – gustavolfm1@hotmail.com</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -2890,7 +2906,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Médico Psiquiatra</t>
+          <t>Médico Psiquiatra – gustavolfm1@hotmail.com</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -3068,7 +3084,11 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Aline Grisi de Lacerda</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>091.447.454-51</t>
@@ -3076,7 +3096,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Psicóloga, Aline Grisi de Lacerda, CPF 091.447.454</t>
+          <t>Psicóloga</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -3097,7 +3117,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3146,11 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>096.817.054-40</t>
@@ -3134,7 +3158,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -3155,7 +3179,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3212,11 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Aline Grisi de Lacerda</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>091.447.454-51</t>
@@ -3196,7 +3224,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Aline Grisi de Lacerda, CPF 091.447.454</t>
+          <t>Entrevistadora Forense</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -3217,7 +3245,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3278,11 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Jamile Silva de Oliveira</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>080.315.474-75</t>
@@ -3258,7 +3290,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Jamile Silva de Oliveira, CPF 080.315.474</t>
+          <t>Entrevistadora Forense</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -3279,7 +3311,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3344,11 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Jamile Silva de Oliveira</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>080.315.474-75</t>
@@ -3320,7 +3356,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Jamile Silva de Oliveira, CPF 080.315.474</t>
+          <t>Entrevistadora Forense</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3341,7 +3377,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -3374,13 +3410,21 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Aline Grisi de Lacerda</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>091.447.454-51</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Entrevistadora Forense</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
@@ -3399,7 +3443,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3584,11 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Aline Grisi de Lacerda</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>091.447.454-51</t>
@@ -3548,7 +3596,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Aline Grisi de Lacerda, CPF 091.447.454</t>
+          <t>Entrevistadora Forense</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3569,7 +3617,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3650,11 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Aline Grisi de Lacerda</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>091.447.454-51</t>
@@ -3610,7 +3662,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Aline Grisi de Lacerda, CPF 091.447.454</t>
+          <t>Entrevistadora Forense</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3631,7 +3683,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3782,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como a comprovação de entrega do laudo pericial em cartório.</t>
+          <t>Interessado:</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -3818,7 +3870,11 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>ALINE GRISE DE LACERDA</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>091.447.454-51</t>
@@ -3826,7 +3882,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, ALINE GRISE DE LACERDA, CPF 091.447.454</t>
+          <t>Entrevistadora Forense</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -3847,7 +3903,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -3946,7 +4002,11 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>096.817.054-40</t>
@@ -3954,7 +4014,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3975,7 +4035,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4262,11 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Jamile Silva de Oliveira</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>080.315.474-75</t>
@@ -4210,7 +4274,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Jamile Silva de Oliveira, CPF 080.315.474</t>
+          <t>Entrevistadora Forense</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -4231,7 +4295,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4614,11 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Fernanda de Araújo Farias</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
           <t>055.325.034-51</t>
@@ -4558,7 +4626,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>Entrevistadora Forense – Psicóloga</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -4579,7 +4647,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -4674,7 +4742,11 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Fernanda de Araújo Farias</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>055.325.034-51</t>
@@ -4682,7 +4754,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>Entrevistadora Forense – Psicóloga</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -4703,7 +4775,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4932,11 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Fernanda de Araújo Farias</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
           <t>055.325.034-51</t>
@@ -4868,7 +4944,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>Entrevistadora Forense – Psicólogo</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -4889,7 +4965,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5122,11 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Fernanda de Araújo Farias</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr">
         <is>
           <t>055.325.034-51</t>
@@ -5054,7 +5134,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>Entrevistadora Forense – Psicóloga</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -5075,7 +5155,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5184,11 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Marah Danielle Queiroz Conserva de Oliveira</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
           <t>028.733.874-67</t>
@@ -5112,7 +5196,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Marah Danielle Queiroz Conserva de Oliveira, CPF 028.733.874</t>
+          <t>Entrevistadora Forense</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -5133,7 +5217,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5308,11 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Marah Danielle Queiroz Conserva de Oliveira</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>028.733.874-67</t>
@@ -5232,7 +5320,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Marah Danielle Queiroz Conserva de Oliveira, CPF 028.733.874</t>
+          <t>Entrevistadora Forense</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -5253,7 +5341,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5428,11 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
           <t>096.817.054-40</t>
@@ -5348,7 +5440,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -5369,7 +5461,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5490,11 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
           <t>096.817.054-40</t>
@@ -5406,7 +5502,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -5427,7 +5523,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5548,11 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr">
         <is>
           <t>096.817.054-40</t>
@@ -5460,7 +5560,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -5481,7 +5581,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem PROCESSO Nº; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5606,11 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>096.817.054-40</t>
@@ -5514,7 +5618,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como a comprovação de entrega do laudo pericial em cartório.</t>
+          <t>Engenheiro de Segurança do Trabalho</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -5535,7 +5639,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem PROCESSO Nº; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6110,11 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr">
         <is>
           <t>096.817.054-40</t>
@@ -6014,7 +6122,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -6035,7 +6143,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6230,11 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J93" t="inlineStr">
         <is>
           <t>096.817.054-40</t>
@@ -6130,7 +6242,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -6151,7 +6263,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6350,11 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr">
         <is>
           <t>096.817.054-40</t>
@@ -6246,7 +6362,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -6267,7 +6383,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6470,11 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J97" t="inlineStr">
         <is>
           <t>096.817.054-40</t>
@@ -6362,7 +6482,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -6383,7 +6503,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6532,11 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr">
         <is>
           <t>096.817.054-40</t>
@@ -6420,7 +6544,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -6441,7 +6565,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6792,11 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>TARCÍSIO BARBALHO CAVALCANTE</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr">
         <is>
           <t>104.161.554-05</t>
@@ -6676,7 +6804,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como certidão dando conta de que a entrevistadora deu integral cumprimento a pauta de audiências designada.</t>
+          <t>Entrevistador Forense Psicólogo</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -6697,7 +6825,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6998,11 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Tarcísio Barbalho Cavalcante</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>104.161.554-05</t>
@@ -6878,7 +7010,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro do Entrevistador Forense Psicólogo Clínica e Neuropsicologia, Tarcísio Barbalho Cavalcante, CPF 104.161.554</t>
+          <t>Entrevistador Forense Psicologia Clínica e Neuropsicologia</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -6899,7 +7031,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -6928,7 +7060,11 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Tarcísio Barbalho Cavalcante</t>
+        </is>
+      </c>
       <c r="J106" t="inlineStr">
         <is>
           <t>104.161.554-05</t>
@@ -6936,7 +7072,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro do Entrevistador Forense Psicólogo Clínica e Neuropsicologia, Tarcísio Barbalho Cavalcante, CPF 104.161.554</t>
+          <t>Entrevistador Forense Psicologia Clínica e Neuropsicologia</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -6957,7 +7093,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem PROCESSO Nº; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -7110,9 +7246,17 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Aline Grisi de Lacerda</t>
+        </is>
+      </c>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Entrevistadora Forense</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
@@ -7131,7 +7275,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem PROCESSO Nº; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7376,7 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Felipe de Paiva Dias</t>
+          <t>INSS</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7242,7 +7386,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Médico</t>
+          <t>Instituto Nacional do Seguro Social</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -7374,7 +7518,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>82, PIS/PASEP 26727954702, nascido em 17/10/1999, pela realização de perícia nos autos da</t>
+          <t>Interessado:</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
@@ -7436,7 +7580,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Engenheiro Civil e de Segurança do Trabalho</t>
+          <t>Interessado: Eduardo de Araújo Leite</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -7560,7 +7704,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>SIGHOP, foi possível constatar que o cadastro da Perita, Carmen Virgínia Albuquerque Almeida, CPF 674.562.004</t>
+          <t>Interessado:</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -7870,7 +8014,11 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Fernanda de Araújo Farias</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr">
         <is>
           <t>055.325.034-51</t>
@@ -7878,7 +8026,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>Entrevistadora Forense Psicóloga</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -7899,7 +8047,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -8002,7 +8150,11 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Fernanda de Araújo Farias</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr">
         <is>
           <t>055.325.034-51</t>
@@ -8010,7 +8162,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>Entrevistadora Forense – Psicólogo</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
@@ -8031,7 +8183,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8336,11 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr">
         <is>
           <t>096.817.054-40</t>
@@ -8192,7 +8348,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -8213,7 +8369,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8398,11 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr">
         <is>
           <t>096.817.054-40</t>
@@ -8250,7 +8410,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -8271,7 +8431,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -8366,7 +8526,11 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Tarcísio Barbalho Cavalcante</t>
+        </is>
+      </c>
       <c r="J129" t="inlineStr">
         <is>
           <t>104.161.554-05</t>
@@ -8374,7 +8538,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como certidão dando conta de que a entrevistadora deu integral cumprimento a pauta de audiências designada.</t>
+          <t>Entrevistador Forense Psicólogo</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -8395,7 +8559,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8650,11 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Fernanda de Araújo Farias</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr">
         <is>
           <t>055.325.034-51</t>
@@ -8494,7 +8662,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>Entrevistadora Forense – Psicóloga</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -8515,7 +8683,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8720,11 @@
           <t>MARIALVA CAVALCANTE</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Mário Márcio Pereira Dias Chaves</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr">
         <is>
           <t>008.141.464-14</t>
@@ -8560,7 +8732,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>SIGHOP, foi possível constatar que o cadastro do Médico Psiquiatra, Mário Márcio Pereira Dias Chaves, CPF 008.141.464</t>
+          <t>Médico Psiquiatra</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -8581,7 +8753,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
@@ -8596,7 +8768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X121"/>
+  <dimension ref="A1:X120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8828,39 +9000,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3ª Vara Cível da Comarca da Capital</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>13ª Vara Cível da Comarca de Capital</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Comarca de Capital</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0086175-97.2012.8.15.2001</t>
+          <t>0812507-45.2021.8.15.2001</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Juízo da 3ª Vara Cível da Comarca da Capital</t>
+          <t>Juízo da 13ª Vara Cível da Comarca de Capital</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>007.401.374-25</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, faltando, apenas, a comprovação de entrega do laudo pericial em cartório, a fim de possibilitar o pagamento respectivo.</t>
-        </is>
-      </c>
+          <t>059.800.624-91</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -8882,7 +9054,7 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
-          <t>005071_46_2025_8_15_SEI_005071_46.2025.8.15.zip</t>
+          <t>009889_67_2025_8_15_SEI_009889_67.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -8894,107 +9066,103 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13ª Vara Cível da Comarca de Capital</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Comarca de Capital</t>
-        </is>
-      </c>
+          <t>9ª Vara Cível</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0812507-45.2021.8.15.2001</t>
+          <t>0823984-70.2018.8.15.2001</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Juízo da 13ª Vara Cível da Comarca de Capital</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>LARISSA BARBOZA UGULINO DE ARAÚJO</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>LUÍZA BORELLA IMOVEIS LTDA   ME</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>059.800.624-91</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>083.433.514-01</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Interessado:</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>R$ 491,86</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>R$ 491,86</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
-          <t>009889_67_2025_8_15_SEI_009889_67.2025.8.15.zip</t>
+          <t>015004_78_2025_8_15_SEI_015004_78.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Sem PERITO</t>
+          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9ª Vara Cível</t>
+          <t>9ª Vara Cível da Comarca da Capital</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0823984-70.2018.8.15.2001</t>
+          <t>0830572-20.2023.8.15.2001</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>LARISSA BARBOZA UGULINO DE ARAÚJO</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>LUÍZA BORELLA IMOVEIS LTDA   ME</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Juízo da 9ª Vara Cível da Comarca da Capital</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Giulliene Pereira Rodrigues</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>083.433.514-01</t>
+          <t>060.498.354-97</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como a comprovação de entrega do laudo pericial em cartório.</t>
+          <t>Engenheira Eletricista</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -9010,53 +9178,53 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
-          <t>015004_78_2025_8_15_SEI_015004_78.2025.8.15.zip</t>
+          <t>015045_42_2025_8_15_SEI_015045_42.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>9ª Vara Cível da Comarca da Capital</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Comarca de Conde</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0830572-20.2023.8.15.2001</t>
+          <t>0800696-73.2025.8.15.0441</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Juízo da 9ª Vara Cível da Comarca da Capital</t>
+          <t>Juízo da Vara Única da Comarca de Conde</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Giulliene Pereira Rodrigues</t>
+          <t>Ana Roberta Borges da Silva</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>060.498.354-97</t>
+          <t>703.933.934-02</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Eletricista</t>
+          <t>Entrevistadora Forense – anarobertaborges26@gmail.com</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -9072,7 +9240,7 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
-          <t>015045_42_2025_8_15_SEI_015045_42.2025.8.15.zip</t>
+          <t>015415_72_2025_8_15_SEI_015415_72.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -9084,37 +9252,49 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2ª Vara Mista da Comarca de Araruna</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Comarca de Conde</t>
+          <t>Comarca de Araruna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0800696-73.2025.8.15.0441</t>
+          <t>0801633-30.2023.8.15.0061</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Juízo da Vara Única da Comarca de Conde</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+          <t>MARIA DO SOCORRO FERREIRA DE LIMA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CLAUDINA DE LIMA SILVA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Mário Márcio Pereira Dias Chaves</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>703.933.934-02</t>
+          <t>008.141.464-14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Ana Roberta Borges da Silva, CPF 703.933.934</t>
+          <t>Perito Médico – mariomarcio.chaves@hotmail.com</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -9130,19 +9310,19 @@
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
-          <t>015415_72_2025_8_15_SEI_015415_72.2025.8.15.zip</t>
+          <t>015425_23_2025_8_15_SEI_015425_23.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -9159,17 +9339,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0801633-30.2023.8.15.0061</t>
+          <t>0801525-69.2021.8.15.0061</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MARIA DO SOCORRO FERREIRA DE LIMA</t>
+          <t>PEDRO DE LIMA RIBEIRO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CLAUDINA DE LIMA SILVA</t>
+          <t>MARIA GOMES DE LIMA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -9200,7 +9380,7 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
-          <t>015425_23_2025_8_15_SEI_015425_23.2025.8.15.zip</t>
+          <t>015430_47_2025_8_15_SEI_015430_47.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -9212,7 +9392,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -9229,17 +9409,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0801525-69.2021.8.15.0061</t>
+          <t>0802926-98.2024.8.15.0061</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PEDRO DE LIMA RIBEIRO</t>
+          <t>JOSAFÁ DA ROCHA FREIRE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>MARIA GOMES DE LIMA</t>
+          <t>PEDRO FREIRE DE ASSIS</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9270,7 +9450,7 @@
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
-          <t>015430_47_2025_8_15_SEI_015430_47.2025.8.15.zip</t>
+          <t>015615_62_2025_8_15_SEI_015615_62.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -9282,49 +9462,49 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2ª Vara Mista da Comarca de Araruna</t>
+          <t>3ª Vara Mista da Comarca de Itaporanga</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Comarca de Araruna</t>
+          <t>Comarca de Itaporanga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0802926-98.2024.8.15.0061</t>
+          <t>0802828-51.2024.8.15.0211</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>JOSAFÁ DA ROCHA FREIRE</t>
+          <t>ELIZABETE LEITE DE SANTANA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PEDRO FREIRE DE ASSIS</t>
+          <t>COSME JACOBINO LEITE</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Mário Márcio Pereira Dias Chaves</t>
+          <t>Silmaria Bezerra Porcino Medeiros</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>008.141.464-14</t>
+          <t>046.618.494-85</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Perito Médico – mariomarcio.chaves@hotmail.com</t>
+          <t>Perita Assistente Social – siwmarya@hotmail.com</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -9340,7 +9520,7 @@
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
-          <t>015615_62_2025_8_15_SEI_015615_62.2025.8.15.zip</t>
+          <t>016110_13_2025_8_15_SEI_016110_13.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -9352,7 +9532,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -9369,19 +9549,15 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0802828-51.2024.8.15.0211</t>
+          <t>0803087-46.2024.8.15.0211</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ELIZABETE LEITE DE SANTANA</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>COSME JACOBINO LEITE</t>
-        </is>
-      </c>
+          <t>Juízo da 3ª Vara Mista da Comarca de Itaporanga</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Silmaria Bezerra Porcino Medeiros</t>
@@ -9394,7 +9570,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Perita Assistente Social – siwmarya@hotmail.com</t>
+          <t>Assistente Social</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -9410,7 +9586,7 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
-          <t>016110_13_2025_8_15_SEI_016110_13.2025.8.15.zip</t>
+          <t>016144_21_2025_8_15_SEI_016144_21.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -9422,7 +9598,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -9439,15 +9615,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0803087-46.2024.8.15.0211</t>
+          <t>0803389-75.2024.8.15.0211</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Juízo da 3ª Vara Mista da Comarca de Itaporanga</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>LUCIANA DE OLIVEIRA ALVES</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>LAILSON DE OLIVEIRA ALVES</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>Silmaria Bezerra Porcino Medeiros</t>
@@ -9476,7 +9656,7 @@
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
-          <t>016144_21_2025_8_15_SEI_016144_21.2025.8.15.zip</t>
+          <t>016155_35_2025_8_15_SEI_016155_35.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -9488,7 +9668,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -9505,22 +9685,22 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0803389-75.2024.8.15.0211</t>
+          <t>0804518-18.2024.8.15.0211</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>LUCIANA DE OLIVEIRA ALVES</t>
+          <t>ROSEMARY GOMES LOPES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>LAILSON DE OLIVEIRA ALVES</t>
+          <t>VANDEMBERG GOMES PEREIRA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Silmaria Bezerra Porcino Medeiros</t>
+          <t>Silmara Bezerra Porcino Medeiros</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -9546,7 +9726,7 @@
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
-          <t>016155_35_2025_8_15_SEI_016155_35.2025.8.15.zip</t>
+          <t>016158_30_2025_8_15_SEI_016158_30.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -9558,7 +9738,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -9575,22 +9755,22 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0804518-18.2024.8.15.0211</t>
+          <t>0802999-08.2024.8.15.0211</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ROSEMARY GOMES LOPES</t>
+          <t>EDILMA BIU PEDRO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>VANDEMBERG GOMES PEREIRA</t>
+          <t>R. C. C. P.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Silmara Bezerra Porcino Medeiros</t>
+          <t>Silmaria Bezerra Porcino Medeiros</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -9616,7 +9796,7 @@
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
-          <t>016158_30_2025_8_15_SEI_016158_30.2025.8.15.zip</t>
+          <t>016178_29_2025_8_15_SEI_016178_29.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -9628,49 +9808,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3ª Vara Mista da Comarca de Itaporanga</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Comarca de Itaporanga</t>
-        </is>
-      </c>
+          <t>1ª Vara Regional de Mangabeira.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0802999-08.2024.8.15.0211</t>
+          <t>0804778-35.2016.8.15.2003</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>EDILMA BIU PEDRO</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>R. C. C. P.</t>
-        </is>
-      </c>
+          <t>Juízo da 1ª Vara Regional de Mangabeira.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Silmaria Bezerra Porcino Medeiros</t>
+          <t>JOELLEN ZANARDINE CORDEIRO – Engenheira Civil –</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>046.618.494-85</t>
+          <t>089.695.184-79</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Assistente Social</t>
+          <t>Engenheira Civil –</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -9686,7 +9858,7 @@
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
-          <t>016178_29_2025_8_15_SEI_016178_29.2025.8.15.zip</t>
+          <t>016774_38_2025_8_15_SEI_016774_38.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -9698,35 +9870,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1ª Vara Regional de Mangabeira.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>2ª Vara Mista da Comarca de Itaporanga</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Comarca de Itaporanga</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0804778-35.2016.8.15.2003</t>
+          <t>0802374-37.2025.8.15.0211</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Juízo da 1ª Vara Regional de Mangabeira.</t>
+          <t>Juízo da 2ª Vara Mista da Comarca de Itaporanga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Aline Grisi de Lacerda</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>089.695.184-79</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>091.447.454-51</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Entrevistadora Forense</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -9740,55 +9924,31 @@
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
-          <t>016774_38_2025_8_15_SEI_016774_38.2025.8.15.zip</t>
+          <t>017509_74_2025_8_15_SEI_017509_74.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2ª Vara Mista da Comarca de Itaporanga</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Comarca de Itaporanga</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0802374-37.2025.8.15.0211</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Juízo da 2ª Vara Mista da Comarca de Itaporanga</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>091.447.454-51</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Aline Grisi de Lacerda, CPF 091.447.454</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -9802,19 +9962,19 @@
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
-          <t>017509_74_2025_8_15_SEI_017509_74.2025.8.15.zip</t>
+          <t>017649_67_2025_8_15_SEI_017649_67.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -9840,7 +10000,7 @@
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
-          <t>017649_67_2025_8_15_SEI_017649_67.2025.8.15.zip</t>
+          <t>017650_33_2025_8_15_SEI_017650_33.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9852,7 +10012,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -9878,7 +10038,7 @@
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
-          <t>017650_33_2025_8_15_SEI_017650_33.2025.8.15.zip</t>
+          <t>017651_96_2025_8_15_SEI_017651_96.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9890,7 +10050,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -9916,7 +10076,7 @@
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
-          <t>017651_96_2025_8_15_SEI_017651_96.2025.8.15.zip</t>
+          <t>017652_62_2025_8_15_SEI_017652_62.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9928,7 +10088,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -9954,7 +10114,7 @@
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
-          <t>017652_62_2025_8_15_SEI_017652_62.2025.8.15.zip</t>
+          <t>017653_28_2025_8_15_SEI_017653_28.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9966,7 +10126,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -9992,7 +10152,7 @@
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
-          <t>017653_28_2025_8_15_SEI_017653_28.2025.8.15.zip</t>
+          <t>017654_91_2025_8_15_SEI_017654_91.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10004,19 +10164,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Comarca de Umbuzeiro</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0800820-16.2024.8.15.0401</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Juízo da Vara Única da Comarca de Umbuzeiro</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>091.447.454-51</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como certidão dando conta de que a entrevistadora deu integral cumprimento a pauta de audiências designada.</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -10030,49 +10210,61 @@
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
-          <t>017654_91_2025_8_15_SEI_017654_91.2025.8.15.zip</t>
+          <t>017961_32_2025_8_15_SEI_017961_32.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>5ª Vara Mista da Comarca de Sousa</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Comarca de Umbuzeiro</t>
+          <t>Comarca de Sousa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0800820-16.2024.8.15.0401</t>
+          <t>0809114-50.2024.8.15.0371</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Juízo da Vara Única da Comarca de Umbuzeiro</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+          <t>JOSE DE SA SARMENTO</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Banco C6 Consignado</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Felipe Queiroga Gadelha</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>091.447.454-51</t>
+          <t>021.205.144-02</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como certidão dando conta de que a entrevistadora deu integral cumprimento a pauta de audiências designada.</t>
+          <t>Perito Grafocopista</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -10088,61 +10280,57 @@
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
-          <t>017961_32_2025_8_15_SEI_017961_32.2025.8.15.zip</t>
+          <t>018077_65_2025_8_15_SEI_018077_65.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5ª Vara Mista da Comarca de Sousa</t>
+          <t>3ª Vara Mista da Comarca de Itaporanga</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Comarca de Sousa</t>
+          <t>Comarca de Itaporanga</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0809114-50.2024.8.15.0371</t>
+          <t>0803249-41.2024.8.15.0211</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>JOSE DE SA SARMENTO</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Banco C6 Consignado</t>
-        </is>
-      </c>
+          <t>Juízo da 3ª Vara Mista da Comarca de Itaporanga</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Felipe Queiroga Gadelha</t>
+          <t>Gustavo Leitão de Figueiredo Medeiros</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>021.205.144-02</t>
+          <t>048.107.964-50</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Perito Grafocopista</t>
+          <t>Médico Psiquiatra – gustavolfm1@hotmail.com</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -10158,7 +10346,7 @@
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
-          <t>018077_65_2025_8_15_SEI_018077_65.2025.8.15.zip</t>
+          <t>018142_86_2025_8_15_SEI_018142_86.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -10170,7 +10358,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -10187,15 +10375,19 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0803249-41.2024.8.15.0211</t>
+          <t>0803648-70.2024.8.15.0211</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Juízo da 3ª Vara Mista da Comarca de Itaporanga</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>FRANCISCO PINTO DA SILVA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ROBERTO PORCINO DA SILVA</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>Gustavo Leitão de Figueiredo Medeiros</t>
@@ -10208,7 +10400,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Médico Psiquiatra</t>
+          <t>Médico Psiquiatra – gustavolfm1@hotmail.com</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -10224,7 +10416,7 @@
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
-          <t>018142_86_2025_8_15_SEI_018142_86.2025.8.15.zip</t>
+          <t>018143_52_2025_8_15_SEI_018143_52.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -10236,49 +10428,45 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3ª Vara Mista da Comarca de Itaporanga</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Comarca de Itaporanga</t>
-        </is>
-      </c>
+          <t>9ª Vara Cível da Comarca da Capital</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0803648-70.2024.8.15.0211</t>
+          <t>0847455-13.2021.8.15.2001</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>FRANCISCO PINTO DA SILVA</t>
+          <t>MARIA DO SOCORRO GOMES FONTES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ROBERTO PORCINO DA SILVA</t>
+          <t>MARIA DE FATIMA CAVALCANTE DE MELO PESSOA FARIAS</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Gustavo Leitão de Figueiredo Medeiros</t>
+          <t>Interessada: Alcimar Alves Fraga</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>048.107.964-50</t>
+          <t>582.834.554-00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Médico Psiquiatra</t>
+          <t>Perito Engenheiro Civil – alcimarfraga702@gmail.com</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -10294,7 +10482,7 @@
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
-          <t>018143_52_2025_8_15_SEI_018143_52.2025.8.15.zip</t>
+          <t>018172_36_2025_8_15_SEI_018172_36.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -10306,45 +10494,41 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2005042413</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>9ª Vara Cível da Comarca da Capital</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>0847455-13.2021.8.15.2001</t>
-        </is>
-      </c>
+          <t>2ª Vara Mista da Comarca de Queimadas</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Comarca de Queimadas</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MARIA DO SOCORRO GOMES FONTES</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>MARIA DE FATIMA CAVALCANTE DE MELO PESSOA FARIAS</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Interessada: Alcimar Alves Fraga</t>
-        </is>
-      </c>
+          <t>Juízo da 2ª Vara Mista da Comarca de Queimadas</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>582.834.554-00</t>
+          <t>055.325.034-51</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Perito Engenheiro Civil – alcimarfraga702@gmail.com</t>
+          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Fernanda de Araújo Farias, CPF 055.325.034</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -10360,53 +10544,53 @@
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
-          <t>018172_36_2025_8_15_SEI_018172_36.2025.8.15.zip</t>
+          <t>018248_71_2025_8_15_SEI_018248_71.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Sem VALOR ARBITRADO</t>
+          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2005042413</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2ª Vara Mista da Comarca de Queimadas</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Comarca de Queimadas</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>Comarca de Jacaraú</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0800545-02.2021.8.15.1071</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Juízo da 2ª Vara Mista da Comarca de Queimadas</t>
+          <t>Juízo da Vara Única da Comarca de Jacaraú</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Aline Grisi de Lacerda</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>055.325.034-51</t>
+          <t>091.447.454-51</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>Psicóloga</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -10422,19 +10606,19 @@
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
-          <t>018248_71_2025_8_15_SEI_018248_71.2025.8.15.zip</t>
+          <t>018259_85_2025_8_15_SEI_018259_85.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -10442,29 +10626,33 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Comarca de Jacaraú</t>
+          <t>Comarca de Sousa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0800545-02.2021.8.15.1071</t>
+          <t>0801804-56.2025.8.15.0371</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Juízo da Vara Única da Comarca de Jacaraú</t>
+          <t>Juizado Especial misto da Comarca de Sousa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>091.447.454-51</t>
+          <t>096.817.054-40</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Psicóloga, Aline Grisi de Lacerda, CPF 091.447.454</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -10480,49 +10668,57 @@
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
-          <t>018259_85_2025_8_15_SEI_018259_85.2025.8.15.zip</t>
+          <t>018356_85_2025_8_15_SEI_018356_85.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2ª Vara Mista da Comarca de Cuité</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Comarca de Sousa</t>
+          <t>Comarca de Cuité</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0801804-56.2025.8.15.0371</t>
+          <t>0801282-77.2025.8.15.0161</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Juizado Especial misto da Comarca de Sousa</t>
+          <t>Juízo da 2ª Vara Mista da Comarca de Cuité</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Aline Grisi de Lacerda</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>096.817.054-40</t>
+          <t>091.447.454-51</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Entrevistadora Forense</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -10538,53 +10734,57 @@
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
-          <t>018356_85_2025_8_15_SEI_018356_85.2025.8.15.zip</t>
+          <t>018373_89_2025_8_15_SEI_018373_89.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2ª Vara Mista da Comarca de Cuité</t>
+          <t>2ª Vara Mista da Comarca de Catolé do Rocha</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Comarca de Cuité</t>
+          <t>Comarca de Catolé do Rocha</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0801282-77.2025.8.15.0161</t>
+          <t>0812004-31.2024.8.15.0251</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Juízo da 2ª Vara Mista da Comarca de Cuité</t>
+          <t>Juízo da 2ª Vara Mista da Comarca de Catolé do Rocha</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Jamile Silva de Oliveira</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>091.447.454-51</t>
+          <t>080.315.474-75</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Aline Grisi de Lacerda, CPF 091.447.454</t>
+          <t>Entrevistadora Forense</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -10600,19 +10800,19 @@
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
-          <t>018373_89_2025_8_15_SEI_018373_89.2025.8.15.zip</t>
+          <t>018388_64_2025_8_15_SEI_018388_64.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -10629,7 +10829,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0812004-31.2024.8.15.0251</t>
+          <t>0804780-81.2024.8.15.0141</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -10638,7 +10838,11 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Jamile Silva de Oliveira</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>080.315.474-75</t>
@@ -10646,7 +10850,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Jamile Silva de Oliveira, CPF 080.315.474</t>
+          <t>Entrevistadora Forense</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -10662,53 +10866,57 @@
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
-          <t>018388_64_2025_8_15_SEI_018388_64.2025.8.15.zip</t>
+          <t>018394_54_2025_8_15_SEI_018394_54.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2ª Vara Mista da Comarca de Catolé do Rocha</t>
+          <t>5ª Vara Mista da Comarca de Santa Rita</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Comarca de Catolé do Rocha</t>
+          <t>Comarca de Santa Rita</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0804780-81.2024.8.15.0141</t>
+          <t>0801525-30.2024.8.15.0331</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Juízo da 2ª Vara Mista da Comarca de Catolé do Rocha</t>
+          <t>Juízo da 5ª Vara Mista da Comarca de Santa Rita</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Aline Grisi de Lacerda</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>080.315.474-75</t>
+          <t>091.447.454-51</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Jamile Silva de Oliveira, CPF 080.315.474</t>
+          <t>Entrevistadora Forense</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -10724,43 +10932,31 @@
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
-          <t>018394_54_2025_8_15_SEI_018394_54.2025.8.15.zip</t>
+          <t>018492_20_2025_8_15_SEI_018492_20.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>5ª Vara Mista da Comarca de Santa Rita</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Comarca de Santa Rita</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0801525-30.2024.8.15.0331</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Juízo da 5ª Vara Mista da Comarca de Santa Rita</t>
-        </is>
-      </c>
+          <t>0806890-65.2024.8.15.0331</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
@@ -10782,7 +10978,7 @@
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
-          <t>018492_20_2025_8_15_SEI_018492_20.2025.8.15.zip</t>
+          <t>018504_97_2025_8_15_SEI_018504_97.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -10794,19 +10990,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2ª Vara Mista da Comarca de Itaporanga</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Comarca de Itaporanga</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0806890-65.2024.8.15.0331</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>0802240-10.2025.8.15.0211</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Juízo 2ª Vara Mista da Comarca de Itaporanga</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
@@ -10814,7 +11022,11 @@
           <t>091.447.454-51</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Aline Grisi de Lacerda, CPF 091.447.454</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -10828,7 +11040,7 @@
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
-          <t>018504_97_2025_8_15_SEI_018504_97.2025.8.15.zip</t>
+          <t>018548_56_2025_8_15_SEI_018548_56.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -10840,7 +11052,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -10857,16 +11069,20 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0802240-10.2025.8.15.0211</t>
+          <t>0802271-30.2025.8.15.0211</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Juízo 2ª Vara Mista da Comarca de Itaporanga</t>
+          <t>Juízo da 2ª Vara Mista da Comarca de Itaporanga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Aline Grisi de Lacerda</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>091.447.454-51</t>
@@ -10874,7 +11090,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Aline Grisi de Lacerda, CPF 091.447.454</t>
+          <t>Entrevistadora Forense</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -10890,19 +11106,19 @@
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
-          <t>018548_56_2025_8_15_SEI_018548_56.2025.8.15.zip</t>
+          <t>018560_36_2025_8_15_SEI_018560_36.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -10919,7 +11135,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0802271-30.2025.8.15.0211</t>
+          <t>0800708-98.2025.8.15.0211</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -10928,7 +11144,11 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Aline Grisi de Lacerda</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>091.447.454-51</t>
@@ -10936,7 +11156,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Aline Grisi de Lacerda, CPF 091.447.454</t>
+          <t>Entrevistadora Forense</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -10952,41 +11172,41 @@
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
-          <t>018560_36_2025_8_15_SEI_018560_36.2025.8.15.zip</t>
+          <t>018563_31_2025_8_15_SEI_018563_31.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2ª Vara Mista da Comarca de Itaporanga</t>
+          <t>2ª Vara Mista da Comarca de Itabaiana</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Comarca de Itaporanga</t>
+          <t>Comarca de Itabaiana</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0800708-98.2025.8.15.0211</t>
+          <t>0802016-81.2024.8.15.0381</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Juízo da 2ª Vara Mista da Comarca de Itaporanga</t>
+          <t>Juízo da 2ª Vara Mista da Comarca de Itabaiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -10998,7 +11218,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Aline Grisi de Lacerda, CPF 091.447.454</t>
+          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Aline Grisi de Lacerda, CPF nº 091.447.454</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -11014,7 +11234,7 @@
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
-          <t>018563_31_2025_8_15_SEI_018563_31.2025.8.15.zip</t>
+          <t>018603_29_2025_8_15_SEI_018603_29.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -11026,41 +11246,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2ª Vara Mista da Comarca de Itabaiana</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Comarca de Itabaiana</t>
-        </is>
-      </c>
+          <t>1ª Vara de Família da Capital</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0802016-81.2024.8.15.0381</t>
+          <t>0859010-90.2022.8.15.2001</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Juízo da 2ª Vara Mista da Comarca de Itabaiana</t>
+          <t>Juízo da 1ª Vara de Família da Capital</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>091.447.454-51</t>
+          <t>008.789.084-47</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Aline Grisi de Lacerda, CPF nº 091.447.454</t>
+          <t>Interessado:</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -11076,7 +11292,7 @@
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
-          <t>018603_29_2025_8_15_SEI_018603_29.2025.8.15.zip</t>
+          <t>018677_35_2025_8_15_SEI_018677_35.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -11088,39 +11304,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1ª Vara de Família da Capital</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>0859010-90.2022.8.15.2001</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Juízo da 1ª Vara de Família da Capital</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>008.789.084-47</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como a comprovação de entrega do laudo pericial em cartório.</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -11134,31 +11330,55 @@
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
-          <t>018677_35_2025_8_15_SEI_018677_35.2025.8.15.zip</t>
+          <t>018726_18_2025_8_15_SEI_018726_18.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Comarca de Soledade</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0801715-88.2025.8.15.0191</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Juízo da Vara Única da Comarca de Soledade</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ALINE GRISE DE LACERDA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>091.447.454-51</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Entrevistadora Forense</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -11172,49 +11392,61 @@
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
-          <t>018726_18_2025_8_15_SEI_018726_18.2025.8.15.zip</t>
+          <t>018731_42_2025_8_15_SEI_018731_42.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2ª Vara Mista da Comarca de Pombal</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Comarca de Soledade</t>
+          <t>Comarca de Pombal</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0801715-88.2025.8.15.0191</t>
+          <t>0802898-94.2021.8.15.0301</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Juízo da Vara Única da Comarca de Soledade</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+          <t>MARDOQUEU ROSADO TRIGUEIRO</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>BANCO CETELEM S/A</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Felipe Queiroga Gadelha</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>091.447.454-51</t>
+          <t>021.205.144-02</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, ALINE GRISE DE LACERDA, CPF 091.447.454</t>
+          <t>Perito Grafocopista–</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -11230,61 +11462,53 @@
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
-          <t>018731_42_2025_8_15_SEI_018731_42.2025.8.15.zip</t>
+          <t>018763_21_2025_8_15_SEI_018763_21.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2ª Vara Mista da Comarca de Pombal</t>
-        </is>
-      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Comarca de Pombal</t>
+          <t>Comarca de Sousa</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0802898-94.2021.8.15.0301</t>
+          <t>0806043-06.2025.8.15.0371</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>MARDOQUEU ROSADO TRIGUEIRO</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>BANCO CETELEM S/A</t>
-        </is>
-      </c>
+          <t>Juizado Especial misto da Comarca de Sousa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Felipe Queiroga Gadelha</t>
+          <t>Eduardo de Araújo Leite</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>021.205.144-02</t>
+          <t>096.817.054-40</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Perito Grafocopista–</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -11300,7 +11524,7 @@
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
-          <t>018763_21_2025_8_15_SEI_018763_21.2025.8.15.zip</t>
+          <t>018893_63_2025_8_15_SEI_018893_63.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -11312,7 +11536,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -11325,16 +11549,20 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0806043-06.2025.8.15.0371</t>
+          <t>0805174-43.2025.8.15.0371</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Juizado Especial misto da Comarca de Sousa</t>
+          <t>Juizado Especial Misto da Comarca de Sousa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>096.817.054-40</t>
@@ -11342,7 +11570,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Engenheiro Civil e de Segurança do Trabalho</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -11358,53 +11586,57 @@
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
-          <t>018893_63_2025_8_15_SEI_018893_63.2025.8.15.zip</t>
+          <t>018894_29_2025_8_15_SEI_018894_29.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2005042413</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1ª Vara Mista da Comarca de Ingá</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Comarca de Sousa</t>
+          <t>Comarca de Ingá</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0805174-43.2025.8.15.0371</t>
+          <t>0801931-87.2023.8.15.0201</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Juizado Especial Misto da Comarca de Sousa</t>
+          <t>Juízo da 1ª Vara Mista da Comarca de Ingá</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Eduardo de Araújo Leite</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>096.817.054-40</t>
+          <t>055.325.034-51</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Engenheiro Civil e de Segurança do Trabalho</t>
+          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Fernanda de Araújo Farias, CPF 055.325.034</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -11420,57 +11652,57 @@
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
-          <t>018894_29_2025_8_15_SEI_018894_29.2025.8.15.zip</t>
+          <t>018905_43_2025_8_15_SEI_018905_43.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Sem VALOR ARBITRADO</t>
+          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2005042413</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1ª Vara Mista da Comarca de Ingá</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Comarca de Ingá</t>
-        </is>
-      </c>
+          <t>1ª Vara Regional de Mangabeira</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0801931-87.2023.8.15.0201</t>
+          <t>0024880-24.2010.8.15.2003</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Juízo da 1ª Vara Mista da Comarca de Ingá</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+          <t>MARIA DAS NEVES RODRIGUES DE LIMA</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>VANIA SOARES</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>JOELLEN ZANARDINE BUSTORFF</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>055.325.034-51</t>
+          <t>089.695.184-79</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>Engenheira Civil</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -11486,57 +11718,57 @@
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
-          <t>018905_43_2025_8_15_SEI_018905_43.2025.8.15.zip</t>
+          <t>018949_02_2025_8_15_SEI_018949_02.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1ª Vara Regional de Mangabeira</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>2ª Vara Mista da Comarca de Catolé do Rocha</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Comarca de Catolé do Rocha</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0024880-24.2010.8.15.2003</t>
+          <t>0804876-33.2023.8.15.0141</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>MARIA DAS NEVES RODRIGUES DE LIMA</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>VANIA SOARES</t>
-        </is>
-      </c>
+          <t>Juízo da 2ª Vara Mista da Comarca de Catolé do Rocha</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>JOELLEN ZANARDINE BUSTORFF</t>
+          <t>Jamile Silva de Oliveira</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>089.695.184-79</t>
+          <t>080.315.474-75</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Engenheira Civil</t>
+          <t>Entrevistadora Forense</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -11552,7 +11784,7 @@
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
-          <t>018949_02_2025_8_15_SEI_018949_02.2025.8.15.zip</t>
+          <t>018983_10_2025_8_15_SEI_018983_10.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -11564,43 +11796,19 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2ª Vara Mista da Comarca de Catolé do Rocha</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Comarca de Catolé do Rocha</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>0804876-33.2023.8.15.0141</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Juízo da 2ª Vara Mista da Comarca de Catolé do Rocha</t>
-        </is>
-      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>080.315.474-75</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Jamile Silva de Oliveira, CPF 080.315.474</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -11614,31 +11822,59 @@
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
-          <t>018983_10_2025_8_15_SEI_018983_10.2025.8.15.zip</t>
+          <t>019056_50_2025_8_15_SEI_019056_50.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Comarca de São Bento</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0000194-63.2015.8.15.1171</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ELIANE MONTEIRO CAMPOS</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>MUNICÍPIO DE PAULISTA</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Sandriele Leite Mota</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>046.618.494-85</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Contadora</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -11652,19 +11888,19 @@
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
-          <t>019056_50_2025_8_15_SEI_019056_50.2025.8.15.zip</t>
+          <t>019069_93_2025_8_15_SEI_019069_93.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -11672,37 +11908,33 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Comarca de São Bento</t>
+          <t>Comarca de Sousa</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0000194-63.2015.8.15.1171</t>
+          <t>0804254-69.2025.8.15.0371</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ELIANE MONTEIRO CAMPOS</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>MUNICÍPIO DE PAULISTA</t>
-        </is>
-      </c>
+          <t>Juizado Especial Misto da Comarca de Sousa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Sandriele Leite Mota</t>
+          <t>Eduardo de Araújo Leite</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>046.618.494-85</t>
+          <t>096.817.054-40</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Contadora</t>
+          <t>Engenheiro Civil e de Segurança do Trabalho</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -11718,7 +11950,7 @@
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
-          <t>019069_93_2025_8_15_SEI_019069_93.2025.8.15.zip</t>
+          <t>019206_91_2025_8_15_SEI_019206_91.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
@@ -11730,41 +11962,41 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Comarca de Sousa</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1ª Vara de Família da Comarca da Capital</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0804254-69.2025.8.15.0371</t>
+          <t>0865118-67.2024.8.15.2001</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Juizado Especial Misto da Comarca de Sousa</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Eduardo de Araújo Leite</t>
-        </is>
-      </c>
+          <t>FERNANDO AUGUSTO MENDES DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>PATRICIA RISELI AZEVEDO DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>096.817.054-40</t>
+          <t>792.879.052-15</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Engenheiro Civil e de Segurança do Trabalho</t>
+          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como a comprovação de entrega do laudo pericial em cartório.</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -11780,53 +12012,49 @@
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
-          <t>019206_91_2025_8_15_SEI_019206_91.2025.8.15.zip</t>
+          <t>019218_71_2025_8_15_SEI_019218_71.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Sem VALOR ARBITRADO</t>
+          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1ª Vara de Família da Comarca da Capital</t>
+          <t>1ª Vara Regional Cível de Mangabeira da Comarca da Capital</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>0865118-67.2024.8.15.2001</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>FERNANDO AUGUSTO MENDES DOS SANTOS</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>PATRICIA RISELI AZEVEDO DOS SANTOS</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Juízo da 1ª Vara Regional Cível de Mangabeira da Comarca da Capital</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Felipe Queiroga Gadelha</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>792.879.052-15</t>
+          <t>021.205.144-02</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como a comprovação de entrega do laudo pericial em cartório.</t>
+          <t>Perito Grafotécnico</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -11842,49 +12070,57 @@
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
-          <t>019218_71_2025_8_15_SEI_019218_71.2025.8.15.zip</t>
+          <t>019296_38_2025_8_15_SEI_019296_38.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem PROCESSO Nº; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>1ª Vara Regional Cível de Mangabeira da Comarca da Capital</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2005042413</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Comarca de Solânea</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0800165-58.2024.8.15.0461</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Juízo da 1ª Vara Regional Cível de Mangabeira da Comarca da Capital</t>
+          <t>Juízo da Vara Única da Comarca de Solânea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Felipe Queiroga Gadelha</t>
+          <t>Fernanda de Araújo Farias</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>021.205.144-02</t>
+          <t>055.325.034-51</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Perito Grafotécnico</t>
+          <t>Entrevistadora Forense – Psicóloga</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -11900,19 +12136,19 @@
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
         <is>
-          <t>019296_38_2025_8_15_SEI_019296_38.2025.8.15.zip</t>
+          <t>019316_37_2025_8_15_SEI_019316_37.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Sem PROCESSO Nº; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -11929,12 +12165,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0800165-58.2024.8.15.0461</t>
+          <t>0800473-94.2024.8.15.0461</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Juízo da Vara Única da Comarca de Solânea</t>
+          <t>Juízo da Vara única da Comarca de Solânea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -11946,7 +12182,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Fernanda de Araújo Farias, CPF 055.325.034</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -11962,7 +12198,7 @@
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
-          <t>019316_37_2025_8_15_SEI_019316_37.2025.8.15.zip</t>
+          <t>019325_22_2025_8_15_SEI_019325_22.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -11974,7 +12210,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -11991,16 +12227,20 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0800473-94.2024.8.15.0461</t>
+          <t>0801059-68.2023.8.15.0461</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Juízo da Vara única da Comarca de Solânea</t>
+          <t>Juízo da Vara Única da Comarca de Solânea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Fernanda de Araújo Farias</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>055.325.034-51</t>
@@ -12008,7 +12248,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>Entrevistadora Forense – Psicóloga</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -12024,19 +12264,19 @@
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
-          <t>019325_22_2025_8_15_SEI_019325_22.2025.8.15.zip</t>
+          <t>019328_17_2025_8_15_SEI_019328_17.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -12053,7 +12293,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0801059-68.2023.8.15.0461</t>
+          <t>0800496-74.2023.8.15.0461</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -12070,7 +12310,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como certidão dando conta de que a entrevistadora deu integral cumprimento a pauta de audiências designada.</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -12086,7 +12326,7 @@
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
-          <t>019328_17_2025_8_15_SEI_019328_17.2025.8.15.zip</t>
+          <t>019330_46_2025_8_15_SEI_019330_46.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -12098,7 +12338,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -12115,12 +12355,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0800496-74.2023.8.15.0461</t>
+          <t>0801674-58.2023.8.15.0461</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Juízo da Vara Única da Comarca de Solânea</t>
+          <t>Juízo da Vara única da Comarca de Solânea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -12132,7 +12372,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como certidão dando conta de que a entrevistadora deu integral cumprimento a pauta de audiências designada.</t>
+          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Fernanda de Araújo Farias, CPF 055.325.034</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -12148,7 +12388,7 @@
       <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
-          <t>019330_46_2025_8_15_SEI_019330_46.2025.8.15.zip</t>
+          <t>019333_41_2025_8_15_SEI_019333_41.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -12160,7 +12400,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -12177,16 +12417,20 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0801674-58.2023.8.15.0461</t>
+          <t>0801101-49.2025.8.15.0461</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Juízo da Vara única da Comarca de Solânea</t>
+          <t>Juízo da Vara Única da Comarca de Solânea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Fernanda de Araújo Farias</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
           <t>055.325.034-51</t>
@@ -12194,7 +12438,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>Entrevistadora Forense – Psicólogo</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -12210,19 +12454,19 @@
       <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
-          <t>019333_41_2025_8_15_SEI_019333_41.2025.8.15.zip</t>
+          <t>019337_02_2025_8_15_SEI_019337_02.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -12239,7 +12483,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0801101-49.2025.8.15.0461</t>
+          <t>0800462-31.2025.8.15.0461</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -12256,7 +12500,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, FERNANDA DE ARAÚJO FARIAS, CPF 055.325.034</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -12272,7 +12516,7 @@
       <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
-          <t>019337_02_2025_8_15_SEI_019337_02.2025.8.15.zip</t>
+          <t>019341_60_2025_8_15_SEI_019341_60.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
@@ -12284,7 +12528,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -12301,7 +12545,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0800462-31.2025.8.15.0461</t>
+          <t>0801404-97.2024.8.15.0461</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -12334,7 +12578,7 @@
       <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
-          <t>019341_60_2025_8_15_SEI_019341_60.2025.8.15.zip</t>
+          <t>019342_26_2025_8_15_SEI_019342_26.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
@@ -12346,7 +12590,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -12363,7 +12607,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0801404-97.2024.8.15.0461</t>
+          <t>0800077-25.2021.8.15.0461</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -12372,7 +12616,11 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Fernanda de Araújo Farias</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
           <t>055.325.034-51</t>
@@ -12380,7 +12628,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, FERNANDA DE ARAÚJO FARIAS, CPF 055.325.034</t>
+          <t>Entrevistadora Forense – Psicóloga</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -12396,53 +12644,53 @@
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
-          <t>019342_26_2025_8_15_SEI_019342_26.2025.8.15.zip</t>
+          <t>019343_89_2025_8_15_SEI_019343_89.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2005042413</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Comarca de Solânea</t>
+          <t>Comarca de Teixeira</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0800077-25.2021.8.15.0461</t>
+          <t>0801128-19.2023.8.15.0391</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Juízo da Vara Única da Comarca de Solânea</t>
+          <t>Juízo da Vara Única da Comarca de Teixeira</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Marah Danielle Queiroz Conserva de Oliveira</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>055.325.034-51</t>
+          <t>028.733.874-67</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>Entrevistadora Forense</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -12458,49 +12706,53 @@
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr">
         <is>
-          <t>019343_89_2025_8_15_SEI_019343_89.2025.8.15.zip</t>
+          <t>019345_21_2025_8_15_SEI_019345_21.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2005042413</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Comarca de Teixeira</t>
+          <t>Comarca de Solânea</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0801128-19.2023.8.15.0391</t>
+          <t>0801376-32.2024.8.15.0461</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Juízo da Vara Única da Comarca de Teixeira</t>
+          <t>Juízo da Vara Única da Comarca de Solânea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>028.733.874-67</t>
+          <t>055.325.034-51</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Marah Danielle Queiroz Conserva de Oliveira, CPF 028.733.874</t>
+          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como certidão dando conta de que a entrevistadora deu integral cumprimento a pauta de audiências designada.</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -12516,7 +12768,7 @@
       <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr">
         <is>
-          <t>019345_21_2025_8_15_SEI_019345_21.2025.8.15.zip</t>
+          <t>019346_84_2025_8_15_SEI_019346_84.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -12528,41 +12780,41 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2005042413</t>
-        </is>
-      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Comarca de Solânea</t>
+          <t>Comarca de Teixeira</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0801376-32.2024.8.15.0461</t>
+          <t>0801035-27.2021.8.15.0391</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Juízo da Vara Única da Comarca de Solânea</t>
+          <t>Juízo da Vara Única da Comarca de Teixeira</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Marah Danielle Queiroz Conserva de Oliveira</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>055.325.034-51</t>
+          <t>028.733.874-67</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como certidão dando conta de que a entrevistadora deu integral cumprimento a pauta de audiências designada.</t>
+          <t>Entrevistadora Forense</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -12578,19 +12830,19 @@
       <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr">
         <is>
-          <t>019346_84_2025_8_15_SEI_019346_84.2025.8.15.zip</t>
+          <t>019348_16_2025_8_15_SEI_019348_16.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -12603,7 +12855,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0801035-27.2021.8.15.0391</t>
+          <t>0801034-42.2021.8.15.0391</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -12620,7 +12872,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Marah Danielle Queiroz Conserva de Oliveira, CPF 028.733.874</t>
+          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, MARAH DANIELLE QUEIROZ CONSERVA DE OLIVEIRA, CPF 028.733.874</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -12636,7 +12888,7 @@
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr">
         <is>
-          <t>019348_16_2025_8_15_SEI_019348_16.2025.8.15.zip</t>
+          <t>019350_45_2025_8_15_SEI_019350_45.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -12648,7 +12900,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -12656,29 +12908,33 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Comarca de Teixeira</t>
+          <t>Comarca de Sousa</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0801034-42.2021.8.15.0391</t>
+          <t>0805281-87.2025.8.15.0371</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Juízo da Vara Única da Comarca de Teixeira</t>
+          <t>Juizado Especial misto da Comarca de Sousa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>028.733.874-67</t>
+          <t>096.817.054-40</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, MARAH DANIELLE QUEIROZ CONSERVA DE OLIVEIRA, CPF 028.733.874</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -12694,19 +12950,19 @@
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr">
         <is>
-          <t>019350_45_2025_8_15_SEI_019350_45.2025.8.15.zip</t>
+          <t>019390_43_2025_8_15_SEI_019390_43.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -12719,7 +12975,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0805281-87.2025.8.15.0371</t>
+          <t>0805181-35.2025.8.15.0371</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -12728,7 +12984,11 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>096.817.054-40</t>
@@ -12736,7 +12996,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -12752,19 +13012,19 @@
       <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr">
         <is>
-          <t>019390_43_2025_8_15_SEI_019390_43.2025.8.15.zip</t>
+          <t>019391_09_2025_8_15_SEI_019391_09.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -12775,18 +13035,18 @@
           <t>Comarca de Sousa</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>0805181-35.2025.8.15.0371</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>Juizado Especial misto da Comarca de Sousa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
           <t>096.817.054-40</t>
@@ -12794,7 +13054,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -12810,19 +13070,19 @@
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
         <is>
-          <t>019391_09_2025_8_15_SEI_019391_09.2025.8.15.zip</t>
+          <t>019393_38_2025_8_15_SEI_019393_38.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem PROCESSO Nº; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -12836,11 +13096,15 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Juizado Especial misto da Comarca de Sousa</t>
+          <t>Juizado Especial Misto da Comarca de Sousa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
           <t>096.817.054-40</t>
@@ -12848,7 +13112,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Engenheiro de Segurança do Trabalho</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -12864,45 +13128,61 @@
       <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr">
         <is>
-          <t>019393_38_2025_8_15_SEI_019393_38.2025.8.15.zip</t>
+          <t>019394_04_2025_8_15_SEI_019394_04.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem PROCESSO Nº; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>3ª Vara Mista da Comarca de Sapé</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Comarca de Sousa</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
+          <t>Comarca de Sapé</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0800309-81.2018.8.15.0351</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Juizado Especial Misto da Comarca de Sousa</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
+          <t>MAGNO PEREIRA DA SILVA</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE SAPE</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Felipe Queiroga Gadelha</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>096.817.054-40</t>
+          <t>021.205.144-02</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como a comprovação de entrega do laudo pericial em cartório.</t>
+          <t>Perito Engenheiro</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -12918,61 +13198,53 @@
       <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr">
         <is>
-          <t>019394_04_2025_8_15_SEI_019394_04.2025.8.15.zip</t>
+          <t>019406_81_2025_8_15_SEI_019406_81.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>3ª Vara Mista da Comarca de Sapé</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2005042413</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Comarca de Sapé</t>
+          <t>Comarca de Solânea</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0800309-81.2018.8.15.0351</t>
+          <t>0801155-49.2024.8.15.0461</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MAGNO PEREIRA DA SILVA</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE SAPE</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Felipe Queiroga Gadelha</t>
-        </is>
-      </c>
+          <t>Juízo da Vara Única da Comarca de Solânea</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>021.205.144-02</t>
+          <t>055.325.034-51</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Perito Engenheiro</t>
+          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como certidão dando conta de que a entrevistadora deu integral cumprimento a pauta de audiências designada.</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -12988,19 +13260,19 @@
       <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr">
         <is>
-          <t>019406_81_2025_8_15_SEI_019406_81.2025.8.15.zip</t>
+          <t>019409_76_2025_8_15_SEI_019409_76.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Sem VALOR ARBITRADO</t>
+          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -13017,7 +13289,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0801155-49.2024.8.15.0461</t>
+          <t>0000496-15.2020.8.15.0461</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -13050,7 +13322,7 @@
       <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr">
         <is>
-          <t>019409_76_2025_8_15_SEI_019409_76.2025.8.15.zip</t>
+          <t>019412_71_2025_8_15_SEI_019412_71.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
@@ -13062,36 +13334,36 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2005042413</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>3ª Vara Regional do Juízo das Garantias da Comarca de Campina Grande</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Comarca de Solânea</t>
+          <t>Comarca de Campina Grande</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0000496-15.2020.8.15.0461</t>
+          <t>0800581-54.2024.8.15.0581</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Juízo da Vara Única da Comarca de Solânea</t>
+          <t>Juízo da 3ª Vara Regional do Juízo das Garantias da Comarca de Campina Grande</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>055.325.034-51</t>
+          <t>091.447.454-51</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -13112,7 +13384,7 @@
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr">
         <is>
-          <t>019412_71_2025_8_15_SEI_019412_71.2025.8.15.zip</t>
+          <t>019418_61_2025_8_15_SEI_019418_61.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
@@ -13124,41 +13396,41 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>3ª Vara Regional do Juízo das Garantias da Comarca de Campina Grande</t>
-        </is>
-      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2005042413</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Comarca de Campina Grande</t>
+          <t>Comarca de Solânea</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0800581-54.2024.8.15.0581</t>
+          <t>0801308-53.2022.8.15.0461</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Juízo da 3ª Vara Regional do Juízo das Garantias da Comarca de Campina Grande</t>
+          <t>Juízo da Vara Única da Comarca de Solânea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>091.447.454-51</t>
+          <t>055.325.034-51</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como certidão dando conta de que a entrevistadora deu integral cumprimento a pauta de audiências designada.</t>
+          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, FERNANDA DE ARAÚJO FARIAS, CPF 055.325.034</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -13174,7 +13446,7 @@
       <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr">
         <is>
-          <t>019418_61_2025_8_15_SEI_019418_61.2025.8.15.zip</t>
+          <t>019419_27_2025_8_15_SEI_019419_27.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
@@ -13186,7 +13458,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -13203,12 +13475,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0801308-53.2022.8.15.0461</t>
+          <t>0800488-97.2023.8.15.0461</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Juízo da Vara Única da Comarca de Solânea</t>
+          <t>Juízo da Vara única da Comarca de Solânea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -13220,7 +13492,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, FERNANDA DE ARAÚJO FARIAS, CPF 055.325.034</t>
+          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Fernanda de Araújo Farias, CPF 055.325.034</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -13236,7 +13508,7 @@
       <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr">
         <is>
-          <t>019419_27_2025_8_15_SEI_019419_27.2025.8.15.zip</t>
+          <t>019423_85_2025_8_15_SEI_019423_85.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
@@ -13248,41 +13520,41 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2005042413</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>5ª Vara Regional do Juízo das Garantias da Comarca de Patos</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Comarca de Solânea</t>
+          <t>Comarca de Patos</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>0800488-97.2023.8.15.0461</t>
+          <t>0800013-05.2024.8.15.0301</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Juízo da Vara única da Comarca de Solânea</t>
+          <t>Juízo 5ª Vara Regional do Juízo das Garantias da Comarca de Patos</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>055.325.034-51</t>
+          <t>080.315.474-75</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Jamile Silva de Oliveira, CPF 080.315.474</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -13298,7 +13570,7 @@
       <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr">
         <is>
-          <t>019423_85_2025_8_15_SEI_019423_85.2025.8.15.zip</t>
+          <t>019434_02_2025_8_15_SEI_019434_02.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
@@ -13310,41 +13582,41 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>5ª Vara Regional do Juízo das Garantias da Comarca de Patos</t>
-        </is>
-      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Comarca de Patos</t>
+          <t>Comarca de Sousa</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0800013-05.2024.8.15.0301</t>
+          <t>0801129-93.2025.8.15.0371</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Juízo 5ª Vara Regional do Juízo das Garantias da Comarca de Patos</t>
+          <t>Juizado Especial misto da Comarca de Sousa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>080.315.474-75</t>
+          <t>096.817.054-40</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Jamile Silva de Oliveira, CPF 080.315.474</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -13360,19 +13632,19 @@
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="inlineStr">
         <is>
-          <t>019434_02_2025_8_15_SEI_019434_02.2025.8.15.zip</t>
+          <t>019444_50_2025_8_15_SEI_019444_50.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -13380,29 +13652,29 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Comarca de Sousa</t>
+          <t>Comarca de Teixeira</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>0801129-93.2025.8.15.0371</t>
+          <t>0800827-04.2025.8.15.0391</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Juizado Especial misto da Comarca de Sousa</t>
+          <t>Juízo da Vara Única da Comarca de Teixeira</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>096.817.054-40</t>
+          <t>028.733.874-67</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como certidão dando conta de que a entrevistadora deu integral cumprimento a pauta de audiências designada.</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -13418,7 +13690,7 @@
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr">
         <is>
-          <t>019444_50_2025_8_15_SEI_019444_50.2025.8.15.zip</t>
+          <t>019450_40_2025_8_15_SEI_019450_40.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
@@ -13430,7 +13702,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -13438,29 +13710,33 @@
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Comarca de Teixeira</t>
+          <t>Comarca de Sousa</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0800827-04.2025.8.15.0391</t>
+          <t>0807839-66.2024.8.15.0371</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Juízo da Vara Única da Comarca de Teixeira</t>
+          <t>Juizado Especial misto da Comarca de Sousa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>028.733.874-67</t>
+          <t>096.817.054-40</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como certidão dando conta de que a entrevistadora deu integral cumprimento a pauta de audiências designada.</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -13476,19 +13752,19 @@
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr">
         <is>
-          <t>019450_40_2025_8_15_SEI_019450_40.2025.8.15.zip</t>
+          <t>019454_98_2025_8_15_SEI_019454_98.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -13496,29 +13772,29 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Comarca de Sousa</t>
+          <t>Comarca de Teixeira</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>0807839-66.2024.8.15.0371</t>
+          <t>0800796-81.2025.8.15.0391</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Juizado Especial misto da Comarca de Sousa</t>
+          <t>Juízo da Vara Única da Comarca de Teixeira</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>096.817.054-40</t>
+          <t>028.733.874-67</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como certidão dando conta de que a entrevistadora deu integral cumprimento a pauta de audiências designada.</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -13534,7 +13810,7 @@
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr">
         <is>
-          <t>019454_98_2025_8_15_SEI_019454_98.2025.8.15.zip</t>
+          <t>019459_25_2025_8_15_SEI_019459_25.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
@@ -13546,7 +13822,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -13554,29 +13830,33 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Comarca de Teixeira</t>
+          <t>Comarca de Sousa</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>0800796-81.2025.8.15.0391</t>
+          <t>0806259-98.2024.8.15.0371</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Juízo da Vara Única da Comarca de Teixeira</t>
+          <t>Juizado Especial misto da Comarca de Sousa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>028.733.874-67</t>
+          <t>096.817.054-40</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como certidão dando conta de que a entrevistadora deu integral cumprimento a pauta de audiências designada.</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -13592,49 +13872,49 @@
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr">
         <is>
-          <t>019459_25_2025_8_15_SEI_019459_25.2025.8.15.zip</t>
+          <t>019466_78_2025_8_15_SEI_019466_78.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>5ª Vara Regional do Juízo das Garantias da Comarca de Patos</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Comarca de Sousa</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>0806259-98.2024.8.15.0371</t>
-        </is>
-      </c>
+          <t>Comarca de Patos</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Juizado Especial misto da Comarca de Sousa</t>
+          <t>Juízo da 5ª Vara Regional do Juízo das Garantias da Comarca de Patos</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>096.817.054-40</t>
+          <t>080.315.474-75</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como certidão dando conta de que a entrevistadora deu integral cumprimento a pauta de audiências designada.</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -13650,49 +13930,53 @@
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr">
         <is>
-          <t>019466_78_2025_8_15_SEI_019466_78.2025.8.15.zip</t>
+          <t>019469_73_2025_8_15_SEI_019469_73.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>5ª Vara Regional do Juízo das Garantias da Comarca de Patos</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Comarca de Patos</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
+          <t>Comarca de Sousa</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>0804302-28.2025.8.15.0371</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Juízo da 5ª Vara Regional do Juízo das Garantias da Comarca de Patos</t>
+          <t>Juizado Especial misto da Comarca de Sousa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>080.315.474-75</t>
+          <t>096.817.054-40</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como certidão dando conta de que a entrevistadora deu integral cumprimento a pauta de audiências designada.</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -13708,19 +13992,19 @@
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr">
         <is>
-          <t>019469_73_2025_8_15_SEI_019469_73.2025.8.15.zip</t>
+          <t>019471_05_2025_8_15_SEI_019471_05.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -13733,7 +14017,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0804302-28.2025.8.15.0371</t>
+          <t>0802809-16.2025.8.15.0371</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -13742,7 +14026,11 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J86" t="inlineStr">
         <is>
           <t>096.817.054-40</t>
@@ -13750,7 +14038,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -13766,49 +14054,53 @@
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr">
         <is>
-          <t>019471_05_2025_8_15_SEI_019471_05.2025.8.15.zip</t>
+          <t>019472_68_2025_8_15_SEI_019472_68.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2ª Vara Mista da Comarca de Itaporanga</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Comarca de Sousa</t>
+          <t>Comarca de Itaporanga</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0802809-16.2025.8.15.0371</t>
+          <t>0801811-43.2025.8.15.0211</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Juizado Especial misto da Comarca de Sousa</t>
+          <t>Juízo da 2ª Vara Mista da Comarca de Itaporanga</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>096.817.054-40</t>
+          <t>091.447.454-51</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Aline Grisi de Lacerda, CPF 091.447.454</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -13824,7 +14116,7 @@
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr">
         <is>
-          <t>019472_68_2025_8_15_SEI_019472_68.2025.8.15.zip</t>
+          <t>019489_72_2025_8_15_SEI_019489_72.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
@@ -13836,7 +14128,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -13886,7 +14178,7 @@
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr">
         <is>
-          <t>019489_72_2025_8_15_SEI_019489_72.2025.8.15.zip</t>
+          <t>019492_67_2025_8_15_SEI_019492_67.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
@@ -13898,7 +14190,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -13915,7 +14207,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>0801811-43.2025.8.15.0211</t>
+          <t>0802123-19.2025.8.15.0211</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -13938,133 +14230,145 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>R$ 438,29</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>R$ 438,29</t>
+        </is>
+      </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr">
         <is>
-          <t>019492_67_2025_8_15_SEI_019492_67.2025.8.15.zip</t>
+          <t>019493_33_2025_8_15_SEI_019493_33.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem PERITO</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>2ª Vara Mista da Comarca de Itaporanga</t>
-        </is>
-      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2035800265</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Comarca de Itaporanga</t>
+          <t>Comarca de Belém</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>0802123-19.2025.8.15.0211</t>
+          <t>0801747-95.2023.8.15.0601</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Juízo da 2ª Vara Mista da Comarca de Itaporanga</t>
+          <t>Juízo da Vara Única da Comarca de Belém</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>TARCÍSIO BARBALHO CAVALCANTE</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>091.447.454-51</t>
+          <t>104.161.554-05</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Aline Grisi de Lacerda, CPF 091.447.454</t>
+          <t>Entrevistador Forense Psicólogo</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>R$ 438,29</t>
-        </is>
-      </c>
+      <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>R$ 438,29</t>
-        </is>
-      </c>
+      <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr">
         <is>
-          <t>019493_33_2025_8_15_SEI_019493_33.2025.8.15.zip</t>
+          <t>019518_56_2025_8_15_SEI_019518_56.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Sem PERITO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>2035800265</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2ª Vara da Comarca de Araruna</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Comarca de Belém</t>
+          <t>Comarca de Araruna</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>0801747-95.2023.8.15.0601</t>
+          <t>0800659-22.2025.8.15.0061</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Juízo da Vara Única da Comarca de Belém</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
+          <t>GENILDA PAULO DA SILVA BEZERRA</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>FRANCISCO DE ASSIS DA SILVA BEZERRA</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Mário Márcio Pereira Dias Chaves</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>104.161.554-05</t>
+          <t>008.141.464-14</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como certidão dando conta de que a entrevistadora deu integral cumprimento a pauta de audiências designada.</t>
+          <t>Perito Médico – mariomarcio.chaves@hotmail.com</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -14080,61 +14384,61 @@
       <c r="V91" t="inlineStr"/>
       <c r="W91" t="inlineStr">
         <is>
-          <t>019518_56_2025_8_15_SEI_019518_56.2025.8.15.zip</t>
+          <t>019523_80_2025_8_15_SEI_019523_80.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2ª Vara da Comarca de Araruna</t>
+          <t>1ª Vara Mista da Comarca de Pombal</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Comarca de Araruna</t>
+          <t>Comarca de Pombal</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>0800659-22.2025.8.15.0061</t>
+          <t>0802115-34.2023.8.15.0301</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>GENILDA PAULO DA SILVA BEZERRA</t>
+          <t>MARIA DE FATIMA SANTOS DE SOUSA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>FRANCISCO DE ASSIS DA SILVA BEZERRA</t>
+          <t>BANCO C6 CONSIGNADO</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Mário Márcio Pereira Dias Chaves</t>
+          <t>Felipe Queiroga Gadelha</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>008.141.464-14</t>
+          <t>021.205.144-02</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Perito Médico – mariomarcio.chaves@hotmail.com</t>
+          <t>Perito Grafocopista</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -14150,7 +14454,7 @@
       <c r="V92" t="inlineStr"/>
       <c r="W92" t="inlineStr">
         <is>
-          <t>019523_80_2025_8_15_SEI_019523_80.2025.8.15.zip</t>
+          <t>019525_12_2025_8_15_SEI_019525_12.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
@@ -14162,49 +14466,45 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>1ª Vara Mista da Comarca de Pombal</t>
-        </is>
-      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2035800265</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Comarca de Pombal</t>
+          <t>Comarca de Belém</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>0802115-34.2023.8.15.0301</t>
+          <t>0801944-16.2024.8.15.0601</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>MARIA DE FATIMA SANTOS DE SOUSA</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>BANCO C6 CONSIGNADO</t>
-        </is>
-      </c>
+          <t>Juízo da Vara Única da Comarca de Belém</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Felipe Queiroga Gadelha</t>
+          <t>Tarcísio Barbalho Cavalcante</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>021.205.144-02</t>
+          <t>104.161.554-05</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Perito Grafocopista</t>
+          <t>Entrevistador Forense Psicologia Clínica e Neuropsicologia</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -14220,7 +14520,7 @@
       <c r="V93" t="inlineStr"/>
       <c r="W93" t="inlineStr">
         <is>
-          <t>019525_12_2025_8_15_SEI_019525_12.2025.8.15.zip</t>
+          <t>019526_75_2025_8_15_SEI_019526_75.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X93" t="inlineStr">
@@ -14232,7 +14532,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -14247,18 +14547,18 @@
           <t>Comarca de Belém</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>0801944-16.2024.8.15.0601</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>Juízo da Vara Única da Comarca de Belém</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Tarcísio Barbalho Cavalcante</t>
+        </is>
+      </c>
       <c r="J94" t="inlineStr">
         <is>
           <t>104.161.554-05</t>
@@ -14266,7 +14566,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro do Entrevistador Forense Psicólogo Clínica e Neuropsicologia, Tarcísio Barbalho Cavalcante, CPF 104.161.554</t>
+          <t>Entrevistador Forense Psicologia Clínica e Neuropsicologia</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -14282,49 +14582,61 @@
       <c r="V94" t="inlineStr"/>
       <c r="W94" t="inlineStr">
         <is>
-          <t>019526_75_2025_8_15_SEI_019526_75.2025.8.15.zip</t>
+          <t>019532_65_2025_8_15_SEI_019532_65.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem PROCESSO Nº; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>2035800265</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2ª Vara da Comarca de Araruna</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Comarca de Belém</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
+          <t>Comarca de Araruna</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0800930-65.2024.8.15.0061</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Juízo da Vara Única da Comarca de Belém</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
+          <t>FRANCISCA PEREIRA FRANCO SILVA</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ALDINETE DANTAS PEREIRA</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Felipe Queiroga Gadelha</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>104.161.554-05</t>
+          <t>021.205.144-02</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro do Entrevistador Forense Psicólogo Clínica e Neuropsicologia, Tarcísio Barbalho Cavalcante, CPF 104.161.554</t>
+          <t>Grafotécnico</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -14340,89 +14652,77 @@
       <c r="V95" t="inlineStr"/>
       <c r="W95" t="inlineStr">
         <is>
-          <t>019532_65_2025_8_15_SEI_019532_65.2025.8.15.zip</t>
+          <t>019534_94_2025_8_15_SEI_019534_94.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>2ª Vara da Comarca de Araruna</t>
-        </is>
-      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Comarca de Araruna</t>
+          <t>Comarca de Santa Luzia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>0800930-65.2024.8.15.0061</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>FRANCISCA PEREIRA FRANCO SILVA</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>ALDINETE DANTAS PEREIRA</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Felipe Queiroga Gadelha</t>
-        </is>
-      </c>
+          <t>0801418-16.2024.8.15.0321</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
-          <t>021.205.144-02</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Grafotécnico</t>
-        </is>
-      </c>
+          <t>091.447.454-51</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>R$ 438,29</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>R$ 438,29</t>
+        </is>
+      </c>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
       <c r="W96" t="inlineStr">
         <is>
-          <t>019534_94_2025_8_15_SEI_019534_94.2025.8.15.zip</t>
+          <t>019535_60_2025_8_15_SEI_019535_60.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Sem VALOR ARBITRADO</t>
+          <t>Sem PERITO</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -14433,54 +14733,50 @@
           <t>Comarca de Santa Luzia</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>0801418-16.2024.8.15.0321</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Juízo da Vara Única da Comarca de Santa Luzia</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>091.447.454-51</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Aline Grisi de Lacerda</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Entrevistadora Forense</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>R$ 438,29</t>
-        </is>
-      </c>
+      <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr">
-        <is>
-          <t>R$ 438,29</t>
-        </is>
-      </c>
+      <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
       <c r="W97" t="inlineStr">
         <is>
-          <t>019535_60_2025_8_15_SEI_019535_60.2025.8.15.zip</t>
+          <t>019537_89_2025_8_15_SEI_019537_89.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Sem PERITO</t>
+          <t>Sem PROCESSO Nº; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -14491,7 +14787,11 @@
           <t>Comarca de Santa Luzia</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0801418-16.2024.8.15.0321</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>Juízo da Vara Única da Comarca de Santa Luzia</t>
@@ -14499,138 +14799,154 @@
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>091.447.454-51</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Aline Grisi de Lacerda, CPF 091.447.454</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>R$ 438,29</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>R$ 438,29</t>
+        </is>
+      </c>
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
       <c r="W98" t="inlineStr">
         <is>
-          <t>019537_89_2025_8_15_SEI_019537_89.2025.8.15.zip</t>
+          <t>019540_84_2025_8_15_SEI_019540_84.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem PERITO</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2ª Vara Mista da Comarca de Cabedelo</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Comarca de Santa Luzia</t>
+          <t>Comarca de Cabedelo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>0801418-16.2024.8.15.0321</t>
+          <t>0802956-63.2024.8.15.0731</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Juízo da Vara Única da Comarca de Santa Luzia</t>
+          <t>Juízo da 2ª Vara Mista da Comarca de Cabedelo</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>INSS</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>091.447.454-51</t>
+          <t>051.287.504-93</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Aline Grisi de Lacerda, CPF 091.447.454</t>
+          <t>Instituto Nacional do Seguro Social</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>R$ 438,29</t>
-        </is>
-      </c>
+      <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr">
-        <is>
-          <t>R$ 438,29</t>
-        </is>
-      </c>
+      <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
       <c r="W99" t="inlineStr">
         <is>
-          <t>019540_84_2025_8_15_SEI_019540_84.2025.8.15.zip</t>
+          <t>019583_77_2025_8_15_SEI_019583_77.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Sem PERITO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>2ª Vara Mista da Comarca de Cabedelo</t>
-        </is>
-      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Comarca de Cabedelo</t>
+          <t>Comarca de São Bento</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>0802956-63.2024.8.15.0731</t>
+          <t>0000185-04.2015.8.15.1171</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Juízo da 2ª Vara Mista da Comarca de Cabedelo</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>JOSE GARCIA FILHO</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE PAULISTA</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Felipe de Paiva Dias</t>
+          <t>Talita Pires Figueiredo</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>051.287.504-93</t>
+          <t>082.246.654-61</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Médico</t>
+          <t>Perita contadora</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -14646,7 +14962,7 @@
       <c r="V100" t="inlineStr"/>
       <c r="W100" t="inlineStr">
         <is>
-          <t>019583_77_2025_8_15_SEI_019583_77.2025.8.15.zip</t>
+          <t>019608_03_2025_8_15_SEI_019608_03.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X100" t="inlineStr">
@@ -14658,45 +14974,45 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2ª Vara Mista da Comarca de São João do Rio do Peixe</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Comarca de São Bento</t>
+          <t>Comarca de São João do Rio do Peixe</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>0000185-04.2015.8.15.1171</t>
+          <t>0802246-46.2024.8.15.0051</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>JOSE GARCIA FILHO</t>
+          <t>RITA DE CÁSSIA MOREIRA DA SILVA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>MUNICIPIO DE PAULISTA</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Talita Pires Figueiredo</t>
-        </is>
-      </c>
+          <t>MARIA MOREIRA</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
-          <t>082.246.654-61</t>
+          <t>117.480.454-82</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Perita contadora</t>
+          <t>Interessado:</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -14712,57 +15028,53 @@
       <c r="V101" t="inlineStr"/>
       <c r="W101" t="inlineStr">
         <is>
-          <t>019608_03_2025_8_15_SEI_019608_03.2025.8.15.zip</t>
+          <t>019648_98_2025_8_15_SEI_019648_98.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>Sem VALOR ARBITRADO</t>
+          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>2ª Vara Mista da Comarca de São João do Rio do Peixe</t>
-        </is>
-      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Comarca de São João do Rio do Peixe</t>
+          <t>Comarca de Sousa</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>0802246-46.2024.8.15.0051</t>
+          <t>0804801-12.2025.8.15.0371</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>RITA DE CÁSSIA MOREIRA DA SILVA</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>MARIA MOREIRA</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>Juizado Especial Misto da Comarca de Sousa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>117.480.454-82</t>
+          <t>096.817.054-40</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>82, PIS/PASEP 26727954702, nascido em 17/10/1999, pela realização de perícia nos autos da</t>
+          <t>Interessado: Eduardo de Araújo Leite</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -14778,19 +15090,19 @@
       <c r="V102" t="inlineStr"/>
       <c r="W102" t="inlineStr">
         <is>
-          <t>019648_98_2025_8_15_SEI_019648_98.2025.8.15.zip</t>
+          <t>019677_82_2025_8_15_SEI_019677_82.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -14803,7 +15115,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>0804801-12.2025.8.15.0371</t>
+          <t>0805172-73.2025.8.15.0371</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -14840,7 +15152,7 @@
       <c r="V103" t="inlineStr"/>
       <c r="W103" t="inlineStr">
         <is>
-          <t>019677_82_2025_8_15_SEI_019677_82.2025.8.15.zip</t>
+          <t>019678_48_2025_8_15_SEI_019678_48.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
@@ -14852,146 +15164,138 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Comarca de Sousa</t>
-        </is>
-      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2ª Vara Regional Cível de Mangabeira</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>0805172-73.2025.8.15.0371</t>
+          <t>0803293-97.2016.8.15.2003</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Juizado Especial Misto da Comarca de Sousa</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Eduardo de Araújo Leite</t>
-        </is>
-      </c>
+          <t>ROSYRIS PRUDENCIO DINIZ PEREIRA</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>WILSON AUGUSTO DA SILVA</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>096.817.054-40</t>
+          <t>674.562.004-91</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Engenheiro Civil e de Segurança do Trabalho</t>
+          <t>Interessado:</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>R$ 830,00</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="inlineStr"/>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>R$ 830,00</t>
+        </is>
+      </c>
       <c r="S104" t="inlineStr"/>
       <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
       <c r="W104" t="inlineStr">
         <is>
-          <t>019678_48_2025_8_15_SEI_019678_48.2025.8.15.zip</t>
+          <t>019718_46_2025_8_15_SEI_019718_46.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>Sem VALOR ARBITRADO</t>
+          <t>Sem PERITO</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2ª Vara Regional Cível de Mangabeira</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>0803293-97.2016.8.15.2003</t>
-        </is>
-      </c>
+          <t>2ª Vara Mista da Comarca de Ingá</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Comarca de Ingá</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>ROSYRIS PRUDENCIO DINIZ PEREIRA</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>WILSON AUGUSTO DA SILVA</t>
-        </is>
-      </c>
+          <t>Juízo da 2ª Vara Mista da Comarca de Ingá</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>674.562.004-91</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>SIGHOP, foi possível constatar que o cadastro da Perita, Carmen Virgínia Albuquerque Almeida, CPF 674.562.004</t>
-        </is>
-      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>R$ 830,00</t>
-        </is>
-      </c>
+      <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="inlineStr">
-        <is>
-          <t>R$ 830,00</t>
-        </is>
-      </c>
+      <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
       <c r="W105" t="inlineStr">
         <is>
-          <t>019718_46_2025_8_15_SEI_019718_46.2025.8.15.zip</t>
+          <t>019720_75_2025_8_15_SEI_019720_75.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>Sem PERITO</t>
+          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2005042413</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2ª Vara Mista da Comarca de Ingá</t>
+          <t>1ª Vara Mista da Comarca de Ingá</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -14999,16 +15303,28 @@
           <t>Comarca de Ingá</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>0802446-54.2025.8.15.0201</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Juízo da 2ª Vara Mista da Comarca de Ingá</t>
+          <t>Juízo da 1ª Vara Mista da Comarca de Ingá</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>055.325.034-51</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Fernanda de Araújo Farias, CPF 055.325.034</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
@@ -15022,19 +15338,19 @@
       <c r="V106" t="inlineStr"/>
       <c r="W106" t="inlineStr">
         <is>
-          <t>019720_75_2025_8_15_SEI_019720_75.2025.8.15.zip</t>
+          <t>019723_70_2025_8_15_SEI_019723_70.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>Sem PROCESSO Nº; Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -15045,7 +15361,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>1ª Vara Mista da Comarca de Ingá</t>
+          <t>1ª Vara da Comarca de Ingá</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -15055,12 +15371,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>0802446-54.2025.8.15.0201</t>
+          <t>0802287-14.2025.8.15.0201</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Juízo da 1ª Vara Mista da Comarca de Ingá</t>
+          <t>Juízo da 1ª Vara da Comarca de Ingá</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -15088,7 +15404,7 @@
       <c r="V107" t="inlineStr"/>
       <c r="W107" t="inlineStr">
         <is>
-          <t>019723_70_2025_8_15_SEI_019723_70.2025.8.15.zip</t>
+          <t>019731_89_2025_8_15_SEI_019731_89.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
@@ -15100,45 +15416,41 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>2005042413</t>
-        </is>
-      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>1ª Vara da Comarca de Ingá</t>
+          <t>2ª Vara Mista da Comarca de Araruna</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Comarca de Ingá</t>
+          <t>Comarca de Araruna</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>0802287-14.2025.8.15.0201</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Juízo da 1ª Vara da Comarca de Ingá</t>
-        </is>
-      </c>
+          <t>0801360-17.2024.8.15.0061</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>MÁRIO MÁRCIO PEREIRA DIAS CHAVES</t>
+        </is>
+      </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>055.325.034-51</t>
+          <t>008.141.464-14</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>Médico Psiquiátrico</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -15154,53 +15466,61 @@
       <c r="V108" t="inlineStr"/>
       <c r="W108" t="inlineStr">
         <is>
-          <t>019731_89_2025_8_15_SEI_019731_89.2025.8.15.zip</t>
+          <t>019753_20_2025_8_15_SEI_019753_20.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr"/>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2005042413</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2ª Vara Mista da Comarca de Araruna</t>
+          <t>1ª Vara da Comarca de Ingá</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Comarca de Araruna</t>
+          <t>Comarca de Ingá</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>0801360-17.2024.8.15.0061</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr"/>
+          <t>0802409-27.2025.8.15.0201</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Juízo da 1ª Vara da Comarca de Ingá</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
-          <t>MÁRIO MÁRCIO PEREIRA DIAS CHAVES</t>
+          <t>Fernanda de Araújo Farias</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>008.141.464-14</t>
+          <t>055.325.034-51</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Médico Psiquiátrico</t>
+          <t>Entrevistadora Forense Psicóloga</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -15216,7 +15536,7 @@
       <c r="V109" t="inlineStr"/>
       <c r="W109" t="inlineStr">
         <is>
-          <t>019753_20_2025_8_15_SEI_019753_20.2025.8.15.zip</t>
+          <t>019827_26_2025_8_15_SEI_019827_26.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
@@ -15228,45 +15548,45 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>2005042413</t>
-        </is>
-      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>1ª Vara da Comarca de Ingá</t>
+          <t>5ª Vara Mista da Comarca de Patos</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Comarca de Ingá</t>
+          <t>Comarca de Patos</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>0802409-27.2025.8.15.0201</t>
+          <t>0804912-36.2023.8.15.0251</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Juízo da 1ª Vara da Comarca de Ingá</t>
+          <t>Juízo da 5ª Vara Mista da Comarca de Patos</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Felipe Queiroga Gadelha</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>055.325.034-51</t>
+          <t>021.205.144-02</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>Perito Grafocopista</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -15282,57 +15602,61 @@
       <c r="V110" t="inlineStr"/>
       <c r="W110" t="inlineStr">
         <is>
-          <t>019827_26_2025_8_15_SEI_019827_26.2025.8.15.zip</t>
+          <t>019830_21_2025_8_15_SEI_019830_21.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr"/>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2005042413</t>
+        </is>
+      </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>5ª Vara Mista da Comarca de Patos</t>
+          <t>2ª Vara Mista da Comarca de Esperança</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Comarca de Patos</t>
+          <t>Comarca de Esperança</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>0804912-36.2023.8.15.0251</t>
+          <t>0000421-41.2018.8.15.0171</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Juízo da 5ª Vara Mista da Comarca de Patos</t>
+          <t>Juízo da 2ª Vara Mista da Comarca de Esperança</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Felipe Queiroga Gadelha</t>
+          <t>Fernanda de Araújo Farias</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>021.205.144-02</t>
+          <t>055.325.034-51</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Perito Grafocopista</t>
+          <t>Entrevistadora Forense – Psicólogo</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -15348,7 +15672,7 @@
       <c r="V111" t="inlineStr"/>
       <c r="W111" t="inlineStr">
         <is>
-          <t>019830_21_2025_8_15_SEI_019830_21.2025.8.15.zip</t>
+          <t>019837_74_2025_8_15_SEI_019837_74.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
@@ -15360,45 +15684,41 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>2005042413</t>
-        </is>
-      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2ª Vara Mista da Comarca de Esperança</t>
+          <t>2ª Vara Mista da Comarca de Itabaiana</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Comarca de Esperança</t>
+          <t>Comarca de Itabaiana</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>0000421-41.2018.8.15.0171</t>
+          <t>0800190-70.2025.8.15.2002</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Juízo da 2ª Vara Mista da Comarca de Esperança</t>
+          <t>Juízo da 2ª Vara Mista da Comarca de Itabaiana</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>055.325.034-51</t>
+          <t>091.447.454-51</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Aline Grisi de Lacerda, CPF 091.447.454</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -15414,7 +15734,7 @@
       <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr">
         <is>
-          <t>019837_74_2025_8_15_SEI_019837_74.2025.8.15.zip</t>
+          <t>019839_06_2025_8_15_SEI_019839_06.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
@@ -15426,7 +15746,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -15443,7 +15763,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>0800190-70.2025.8.15.2002</t>
+          <t>0803178-48.2023.8.15.0381</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -15476,7 +15796,7 @@
       <c r="V113" t="inlineStr"/>
       <c r="W113" t="inlineStr">
         <is>
-          <t>019839_06_2025_8_15_SEI_019839_06.2025.8.15.zip</t>
+          <t>019842_98_2025_8_15_SEI_019842_98.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X113" t="inlineStr">
@@ -15488,41 +15808,41 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>2ª Vara Mista da Comarca de Itabaiana</t>
-        </is>
-      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Comarca de Itabaiana</t>
+          <t>Comarca de Sousa</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>0803178-48.2023.8.15.0381</t>
+          <t>0805282-72.2025.8.15.0371</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Juízo da 2ª Vara Mista da Comarca de Itabaiana</t>
+          <t>Juizado Especial misto da Comarca de Sousa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>091.447.454-51</t>
+          <t>096.817.054-40</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Psicóloga, Aline Grisi de Lacerda, CPF 091.447.454</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -15538,19 +15858,19 @@
       <c r="V114" t="inlineStr"/>
       <c r="W114" t="inlineStr">
         <is>
-          <t>019842_98_2025_8_15_SEI_019842_98.2025.8.15.zip</t>
+          <t>019882_96_2025_8_15_SEI_019882_96.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -15563,7 +15883,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>0805282-72.2025.8.15.0371</t>
+          <t>0804342-10.2025.8.15.0371</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -15572,7 +15892,11 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Eduardo de Araújo Leite</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr">
         <is>
           <t>096.817.054-40</t>
@@ -15580,7 +15904,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Engenheiro</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
@@ -15596,19 +15920,19 @@
       <c r="V115" t="inlineStr"/>
       <c r="W115" t="inlineStr">
         <is>
-          <t>019882_96_2025_8_15_SEI_019882_96.2025.8.15.zip</t>
+          <t>019888_86_2025_8_15_SEI_019888_86.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -15616,29 +15940,33 @@
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Comarca de Sousa</t>
+          <t>Comarca de Pocinhos</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>0804342-10.2025.8.15.0371</t>
+          <t>0800443-76.2025.8.15.0541</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Juizado Especial misto da Comarca de Sousa</t>
+          <t>Juízo da Vara Única da Comarca de Pocinhos</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Aline Santos Soares</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>096.817.054-40</t>
+          <t>039.079.754-56</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>40, PIS/PASEP 14770144764, nascido em 12/05/1993, pela realização de perícia nos autos da</t>
+          <t>Psicóloga</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -15654,23 +15982,27 @@
       <c r="V116" t="inlineStr"/>
       <c r="W116" t="inlineStr">
         <is>
-          <t>019888_86_2025_8_15_SEI_019888_86.2025.8.15.zip</t>
+          <t>019912_46_2025_8_15_SEI_019912_46.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr"/>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2035800265</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
@@ -15679,7 +16011,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>0800443-76.2025.8.15.0541</t>
+          <t>0800813-55.2025.8.15.0541</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -15690,17 +16022,17 @@
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Aline Santos Soares</t>
+          <t>Tarcísio Barbalho Cavalcante</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>039.079.754-56</t>
+          <t>104.161.554-05</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Psicóloga</t>
+          <t>Entrevistador Forense Psicólogo</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -15716,7 +16048,7 @@
       <c r="V117" t="inlineStr"/>
       <c r="W117" t="inlineStr">
         <is>
-          <t>019912_46_2025_8_15_SEI_019912_46.2025.8.15.zip</t>
+          <t>020003_56_2025_8_15_SEI_020003_56.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
@@ -15728,15 +16060,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>2035800265</t>
-        </is>
-      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
@@ -15745,7 +16073,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>0800813-55.2025.8.15.0541</t>
+          <t>0801009-25.2025.8.15.0541</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -15757,12 +16085,12 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>104.161.554-05</t>
+          <t>047.568.134-70</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>se que o feito se encontra devidamente instruído e obedece às normas legais previstas na Resolução 09/2017, ou seja, constam no presente feito: (1) número do processo ordinário; (2) nome e CPF das partes; (3) valor dos honorários finais; (4) endereço, telefone, inscrição no INSS, número da conta bancária do perito; (5) declaração judicial de reconhecimento do direito à Justiça Gratuita; (6) natureza e característica da atividade desempenhada pelo auxiliar do Juízo, bem como certidão dando conta de que a entrevistadora deu integral cumprimento a pauta de audiências designada.</t>
+          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Assistente Social, Poliana Gragen de Vasconcelos Ferreira, CPF 047.568.134</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -15778,7 +16106,7 @@
       <c r="V118" t="inlineStr"/>
       <c r="W118" t="inlineStr">
         <is>
-          <t>020003_56_2025_8_15_SEI_020003_56.2025.8.15.zip</t>
+          <t>020006_51_2025_8_15_SEI_020006_51.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
@@ -15790,37 +16118,45 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
-      <c r="C119" t="inlineStr"/>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2005042413</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Comarca de Pocinhos</t>
+          <t>Comarca de Alagoinha</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>0801009-25.2025.8.15.0541</t>
+          <t>0804093-31.2024.8.15.0521</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Juízo da Vara Única da Comarca de Pocinhos</t>
+          <t>Juízo da Vara Única da Comarca de Alagoinha</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Fernanda de Araújo Farias</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>047.568.134-70</t>
+          <t>055.325.034-51</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense Assistente Social, Poliana Gragen de Vasconcelos Ferreira, CPF 047.568.134</t>
+          <t>Entrevistadora Forense – Psicóloga</t>
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
@@ -15836,53 +16172,61 @@
       <c r="V119" t="inlineStr"/>
       <c r="W119" t="inlineStr">
         <is>
-          <t>020006_51_2025_8_15_SEI_020006_51.2025.8.15.zip</t>
+          <t>020013_07_2025_8_15_SEI_020013_07.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>2005042413</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2ª Vara Mista da Comarca de Araruna</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Comarca de Alagoinha</t>
+          <t>Comarca de Araruna</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>0804093-31.2024.8.15.0521</t>
+          <t>0800916-47.2025.8.15.0061</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Juízo da Vara Única da Comarca de Alagoinha</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
+          <t>FERNANDA CAVALCANTE DA SILVA</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>MARIALVA CAVALCANTE</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Mário Márcio Pereira Dias Chaves</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>055.325.034-51</t>
+          <t>008.141.464-14</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>SIGHOP, é possível constatar que o cadastro da Entrevistadora Forense, Fernanda de Araújo Farias, CPF 055.325.034</t>
+          <t>Médico Psiquiatra</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -15898,78 +16242,12 @@
       <c r="V120" t="inlineStr"/>
       <c r="W120" t="inlineStr">
         <is>
-          <t>020013_07_2025_8_15_SEI_020013_07.2025.8.15.zip</t>
+          <t>020326_35_2025_8_15_SEI_020326_35.2025.8.15.zip</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr"/>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>2ª Vara Mista da Comarca de Araruna</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Comarca de Araruna</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>0800916-47.2025.8.15.0061</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>FERNANDA CAVALCANTE DA SILVA</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>MARIALVA CAVALCANTE</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>008.141.464-14</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>SIGHOP, foi possível constatar que o cadastro do Médico Psiquiatra, Mário Márcio Pereira Dias Chaves, CPF 008.141.464</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
-      <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr"/>
-      <c r="T121" t="inlineStr"/>
-      <c r="U121" t="inlineStr"/>
-      <c r="V121" t="inlineStr"/>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>020326_35_2025_8_15_SEI_020326_35.2025.8.15.zip</t>
-        </is>
-      </c>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>Sem PERITO; Sem VALOR ARBITRADO</t>
+          <t>Sem VALOR ARBITRADO</t>
         </is>
       </c>
     </row>
